--- a/Data/g13.8.xlsx
+++ b/Data/g13.8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.96439345884951</v>
+        <v>11.96582770060558</v>
       </c>
     </row>
     <row r="3">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.01231279225067</v>
+        <v>11.97356237363959</v>
       </c>
     </row>
     <row r="4">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.74810123988309</v>
+        <v>11.70599199124013</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.88477532307686</v>
+        <v>10.84071243896443</v>
       </c>
     </row>
     <row r="6">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9.108069622139048</v>
+        <v>9.032263685095829</v>
       </c>
     </row>
     <row r="7">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.678321003268797</v>
+        <v>9.652746847417564</v>
       </c>
     </row>
     <row r="8">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.01773407447082</v>
+        <v>8.001179706823077</v>
       </c>
     </row>
     <row r="9">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.97844527129217</v>
+        <v>9.028736239756153</v>
       </c>
     </row>
     <row r="10">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.617084314546272</v>
+        <v>6.599897911123117</v>
       </c>
     </row>
     <row r="11">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.825615709242955</v>
+        <v>7.787070507450794</v>
       </c>
     </row>
     <row r="12">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8.845564513098513</v>
+        <v>8.859857473132625</v>
       </c>
     </row>
     <row r="13">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9.163481684623161</v>
+        <v>9.143685441195133</v>
       </c>
     </row>
     <row r="14">
@@ -698,16 +698,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Não estuda e não trabalha</t>
+          <t>Estuda e trabalha</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>31/12/2012</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>24.17739343890454</v>
+        <v>9.682364068073488</v>
       </c>
     </row>
     <row r="15">
@@ -723,11 +723,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>31/12/2013</t>
+          <t>31/12/2012</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24.46965655933733</v>
+        <v>24.22340546063874</v>
       </c>
     </row>
     <row r="16">
@@ -743,11 +743,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31/12/2014</t>
+          <t>31/12/2013</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>23.59892623261636</v>
+        <v>24.52260832718279</v>
       </c>
     </row>
     <row r="17">
@@ -763,11 +763,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>31/12/2015</t>
+          <t>31/12/2014</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25.48512682232793</v>
+        <v>23.63404389166559</v>
       </c>
     </row>
     <row r="18">
@@ -783,11 +783,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>31/12/2016</t>
+          <t>31/12/2015</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27.70410360891397</v>
+        <v>25.55528314284463</v>
       </c>
     </row>
     <row r="19">
@@ -803,11 +803,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>31/12/2017</t>
+          <t>31/12/2016</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>30.6432617277623</v>
+        <v>27.87741724975137</v>
       </c>
     </row>
     <row r="20">
@@ -823,11 +823,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>31/12/2018</t>
+          <t>31/12/2017</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31.30358229601752</v>
+        <v>30.73187980949513</v>
       </c>
     </row>
     <row r="21">
@@ -843,11 +843,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>31/12/2019</t>
+          <t>31/12/2018</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>27.53910949268757</v>
+        <v>31.34978958607622</v>
       </c>
     </row>
     <row r="22">
@@ -863,11 +863,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>31/12/2020</t>
+          <t>31/12/2019</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>32.40384820561173</v>
+        <v>27.53425958847413</v>
       </c>
     </row>
     <row r="23">
@@ -883,11 +883,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>31/12/2021</t>
+          <t>31/12/2020</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>32.96730095060988</v>
+        <v>32.31050202002471</v>
       </c>
     </row>
     <row r="24">
@@ -903,11 +903,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>31/12/2022</t>
+          <t>31/12/2021</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>27.18082179568713</v>
+        <v>32.97505379805603</v>
       </c>
     </row>
     <row r="25">
@@ -923,11 +923,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>31/12/2023</t>
+          <t>31/12/2022</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>27.01953231074691</v>
+        <v>27.11898162868759</v>
       </c>
     </row>
     <row r="26">
@@ -938,16 +938,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Só estuda</t>
+          <t>Não estuda e não trabalha</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>31/12/2012</t>
+          <t>31/12/2023</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>25.60534787983632</v>
+        <v>26.87570132222146</v>
       </c>
     </row>
     <row r="27">
@@ -958,16 +958,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Só estuda</t>
+          <t>Não estuda e não trabalha</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>31/12/2013</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26.609715927658</v>
+        <v>24.32929539320264</v>
       </c>
     </row>
     <row r="28">
@@ -983,11 +983,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>31/12/2014</t>
+          <t>31/12/2012</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>24.87849391650491</v>
+        <v>25.62430701642132</v>
       </c>
     </row>
     <row r="29">
@@ -1003,11 +1003,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>31/12/2015</t>
+          <t>31/12/2013</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25.64331488326894</v>
+        <v>26.68781488040046</v>
       </c>
     </row>
     <row r="30">
@@ -1023,11 +1023,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>31/12/2016</t>
+          <t>31/12/2014</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>25.77501322845462</v>
+        <v>24.98315340218343</v>
       </c>
     </row>
     <row r="31">
@@ -1043,11 +1043,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>31/12/2017</t>
+          <t>31/12/2015</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>24.63403429099106</v>
+        <v>25.81813976740516</v>
       </c>
     </row>
     <row r="32">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>31/12/2018</t>
+          <t>31/12/2016</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>28.40866137529308</v>
+        <v>25.93601653341085</v>
       </c>
     </row>
     <row r="33">
@@ -1083,11 +1083,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>31/12/2019</t>
+          <t>31/12/2017</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>26.09824277068884</v>
+        <v>25.0273039182603</v>
       </c>
     </row>
     <row r="34">
@@ -1103,11 +1103,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>31/12/2020</t>
+          <t>31/12/2018</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.6261672169715</v>
+        <v>28.87947423748897</v>
       </c>
     </row>
     <row r="35">
@@ -1123,11 +1123,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>31/12/2021</t>
+          <t>31/12/2019</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>26.50874503070254</v>
+        <v>26.48073497960748</v>
       </c>
     </row>
     <row r="36">
@@ -1143,11 +1143,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>31/12/2022</t>
+          <t>31/12/2020</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28.62124638481926</v>
+        <v>30.0133146393255</v>
       </c>
     </row>
     <row r="37">
@@ -1163,11 +1163,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>31/12/2023</t>
+          <t>31/12/2021</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>26.6432472373036</v>
+        <v>26.88217833376401</v>
       </c>
     </row>
     <row r="38">
@@ -1178,16 +1178,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Só trabalha</t>
+          <t>Só estuda</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>31/12/2012</t>
+          <t>31/12/2022</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>38.2528652224094</v>
+        <v>29.07402643570408</v>
       </c>
     </row>
     <row r="39">
@@ -1198,16 +1198,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Só trabalha</t>
+          <t>Só estuda</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>31/12/2013</t>
+          <t>31/12/2023</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>36.90831472075404</v>
+        <v>27.08038340032537</v>
       </c>
     </row>
     <row r="40">
@@ -1218,16 +1218,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Só trabalha</t>
+          <t>Só estuda</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>31/12/2014</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>39.77447861099596</v>
+        <v>24.2705199184941</v>
       </c>
     </row>
     <row r="41">
@@ -1243,11 +1243,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>31/12/2015</t>
+          <t>31/12/2012</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>37.98678297132652</v>
+        <v>38.18645982233473</v>
       </c>
     </row>
     <row r="42">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>31/12/2016</t>
+          <t>31/12/2013</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>37.41281354049283</v>
+        <v>36.81601441877716</v>
       </c>
     </row>
     <row r="43">
@@ -1283,11 +1283,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>31/12/2017</t>
+          <t>31/12/2014</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>35.04438297797804</v>
+        <v>39.6768107149108</v>
       </c>
     </row>
     <row r="44">
@@ -1303,11 +1303,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>31/12/2018</t>
+          <t>31/12/2015</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>32.27002225421842</v>
+        <v>37.78586465078588</v>
       </c>
     </row>
     <row r="45">
@@ -1323,11 +1323,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>31/12/2019</t>
+          <t>31/12/2016</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>37.38420246533144</v>
+        <v>37.15430253174191</v>
       </c>
     </row>
     <row r="46">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>31/12/2020</t>
+          <t>31/12/2017</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>31.3529002628708</v>
+        <v>34.58806942482718</v>
       </c>
     </row>
     <row r="47">
@@ -1363,11 +1363,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>31/12/2021</t>
+          <t>31/12/2018</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>32.69833830944476</v>
+        <v>31.7695564696118</v>
       </c>
     </row>
     <row r="48">
@@ -1383,11 +1383,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>31/12/2022</t>
+          <t>31/12/2019</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>35.3523673063948</v>
+        <v>36.95626919216218</v>
       </c>
     </row>
     <row r="49">
@@ -1403,11 +1403,91 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>31/12/2020</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>31.07628542952682</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Só trabalha</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>31/12/2021</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>32.35569736072931</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Só trabalha</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>31/12/2022</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>34.94713446247558</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Só trabalha</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>31/12/2023</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>37.17373876732625</v>
+      <c r="D52" t="n">
+        <v>36.90022983625806</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Só trabalha</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>31/12/2024</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>41.71782062022998</v>
       </c>
     </row>
   </sheetData>
